--- a/tame_output/ON/bt/strategyON_20230817.xlsx
+++ b/tame_output/ON/bt/strategyON_20230817.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -671,12 +671,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.5%</t>
+          <t>456.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>106.6%</t>
+          <t>105.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>101.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>139.1%</t>
+          <t>138.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>133.6%</t>
+          <t>132.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.2%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1691"/>
+  <dimension ref="A1:G1692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40403,7 +40403,7 @@
         <v>45153</v>
       </c>
       <c r="B1691" t="n">
-        <v>2.87949509783155</v>
+        <v>2.87967671812949</v>
       </c>
       <c r="C1691" t="n">
         <v>2.979269203333789</v>
@@ -40419,6 +40419,29 @@
       </c>
       <c r="G1691" t="n">
         <v>4.285296548092218</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="2" t="n">
+        <v>45154</v>
+      </c>
+      <c r="B1692" t="n">
+        <v>2.859500869275066</v>
+      </c>
+      <c r="C1692" t="n">
+        <v>2.966107540648022</v>
+      </c>
+      <c r="D1692" t="n">
+        <v>1.549117553703122</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>3.585398137815524</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>2.177265483280223</v>
+      </c>
+      <c r="G1692" t="n">
+        <v>4.272466830616158</v>
       </c>
     </row>
   </sheetData>
